--- a/uploads/Bid_file_success_error_newly_updated_(6)_(1).xlsx
+++ b/uploads/Bid_file_success_error_newly_updated_(6)_(1).xlsx
@@ -537,7 +537,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TestSigma_20-03-2026_SC1_4q_787</v>
+        <v>TestSigma_26-03-2026_SC1_30_173</v>
       </c>
       <c r="B2">
         <v>2001</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TestSigma_20-03-2026_SC1_x7_710</v>
+        <v>TestSigma_26-03-2026_SC1_sz_343</v>
       </c>
       <c r="B3">
         <v>2001</v>
@@ -757,7 +757,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TestSigma_20-03-2026_SC1_lb_551</v>
+        <v>TestSigma_26-03-2026_SC1_uu_873</v>
       </c>
       <c r="B4">
         <v>2001</v>
@@ -870,7 +870,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TestSigma_20-03-2026_SC1_xk_813</v>
+        <v>TestSigma_26-03-2026_SC1_kz_856</v>
       </c>
       <c r="B5">
         <v>2001</v>
@@ -983,7 +983,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TestSigma_20-03-2026_SC1_z7_803</v>
+        <v>TestSigma_26-03-2026_SC1_s7_209</v>
       </c>
       <c r="B6">
         <v>2001</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TestSigma_20-03-2026_SC1_qr_392</v>
+        <v>TestSigma_26-03-2026_SC1_w2_285</v>
       </c>
       <c r="B7">
         <v>2001</v>

--- a/uploads/Bid_file_success_error_newly_updated_(6)_(1).xlsx
+++ b/uploads/Bid_file_success_error_newly_updated_(6)_(1).xlsx
@@ -537,7 +537,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TestSigma_26-03-2026_SC1_30_173</v>
+        <v>TestSigma_31-03-2026_SC1_6x_243</v>
       </c>
       <c r="B2">
         <v>2001</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TestSigma_26-03-2026_SC1_sz_343</v>
+        <v>TestSigma_31-03-2026_SC1_6j_276</v>
       </c>
       <c r="B3">
         <v>2001</v>
@@ -757,7 +757,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TestSigma_26-03-2026_SC1_uu_873</v>
+        <v>TestSigma_31-03-2026_SC1_ww_827</v>
       </c>
       <c r="B4">
         <v>2001</v>
@@ -870,7 +870,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TestSigma_26-03-2026_SC1_kz_856</v>
+        <v>TestSigma_31-03-2026_SC1_fu_693</v>
       </c>
       <c r="B5">
         <v>2001</v>
@@ -983,7 +983,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TestSigma_26-03-2026_SC1_s7_209</v>
+        <v>TestSigma_31-03-2026_SC1_6e_466</v>
       </c>
       <c r="B6">
         <v>2001</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TestSigma_26-03-2026_SC1_w2_285</v>
+        <v>TestSigma_31-03-2026_SC1_i4_836</v>
       </c>
       <c r="B7">
         <v>2001</v>
